--- a/24_DS_Gen_Ahm_1/01_Advanced Excel/Oct15.xlsx
+++ b/24_DS_Gen_Ahm_1/01_Advanced Excel/Oct15.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\24_DS_Gen_Ahm_1\Advanced Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\24_DS_Gen_Ahm_1\01_Advanced Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB3866EC-D43C-4E0E-95CA-B0E42A8C8877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6348921B-CF14-40DE-84C6-0EAFC7907D0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -382,14 +382,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -744,18 +744,18 @@
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
-      <c r="M2" s="12"/>
-      <c r="N2" s="12"/>
-      <c r="O2" s="12"/>
-      <c r="P2" s="12"/>
-      <c r="Q2" s="12"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="14"/>
+      <c r="Q2" s="14"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
@@ -2351,7 +2351,7 @@
         <v>2590</v>
       </c>
       <c r="C2">
-        <f>VLOOKUP(A2, Population!$B$1:$F$7, 3, FALSE)</f>
+        <f>VLOOKUP(A2,Population!$B$1:$D$7, 3,FALSE)</f>
         <v>68.7</v>
       </c>
       <c r="D2">
@@ -2375,7 +2375,7 @@
         <v>3196</v>
       </c>
       <c r="C3">
-        <f>VLOOKUP(A3, Population!$B$1:$F$7, 3, FALSE)</f>
+        <f>VLOOKUP(A3,Population!$B$1:$D$7, 3,FALSE)</f>
         <v>68.8</v>
       </c>
       <c r="D3">
@@ -2399,7 +2399,7 @@
         <v>2400</v>
       </c>
       <c r="C4">
-        <f>VLOOKUP(A4, Population!$B$1:$F$7, 3, FALSE)</f>
+        <f>VLOOKUP(A4,Population!$B$1:$D$7, 3,FALSE)</f>
         <v>64.900000000000006</v>
       </c>
       <c r="D4">
@@ -2423,7 +2423,7 @@
         <v>2530</v>
       </c>
       <c r="C5">
-        <f>VLOOKUP(A5, Population!$B$1:$F$7, 3, FALSE)</f>
+        <f>VLOOKUP(A5,Population!$B$1:$D$7, 3,FALSE)</f>
         <v>72.3</v>
       </c>
       <c r="D5">
@@ -2447,7 +2447,7 @@
         <v>2900</v>
       </c>
       <c r="C6">
-        <f>VLOOKUP(A6, Population!$B$1:$F$7, 3, FALSE)</f>
+        <f>VLOOKUP(A6,Population!$B$1:$D$7, 3,FALSE)</f>
         <v>52.2</v>
       </c>
       <c r="D6">
@@ -2471,7 +2471,7 @@
         <v>2850</v>
       </c>
       <c r="C7">
-        <f>VLOOKUP(A7, Population!$B$1:$F$7, 3, FALSE)</f>
+        <f>VLOOKUP(A7,Population!$B$1:$D$7, 3,FALSE)</f>
         <v>60.5</v>
       </c>
       <c r="D7">
@@ -2488,27 +2488,27 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="B11" s="13"/>
-      <c r="D11" s="13" t="s">
+      <c r="B11" s="15"/>
+      <c r="D11" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="E11" s="13"/>
+      <c r="E11" s="15"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>48</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D15" t="s">
         <v>49</v>
       </c>
       <c r="E15">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -2516,15 +2516,15 @@
         <v>50</v>
       </c>
       <c r="B16">
-        <f>MATCH(B15, A1:A7, 0)</f>
-        <v>2</v>
+        <f>MATCH(B15, A1:A7,0)</f>
+        <v>5</v>
       </c>
       <c r="D16" t="s">
         <v>34</v>
       </c>
       <c r="E16" t="str">
         <f>INDEX(A1:A7, E15)</f>
-        <v>Palanpur</v>
+        <v>Rajkot</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="B17">
         <f>MATCH(B15,A2:A7, 0)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -2541,7 +2541,7 @@
         <v>51</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -2555,7 +2555,7 @@
         <v>52</v>
       </c>
       <c r="E19">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -2570,8 +2570,8 @@
         <v>53</v>
       </c>
       <c r="E20">
-        <f>INDEX(A2:E7, E18, E19)</f>
-        <v>1.5</v>
+        <f>INDEX(A1:F7, E18, E19)</f>
+        <v>2400</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
@@ -2603,15 +2603,15 @@
         <v>54</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D26" s="7"/>
       <c r="E26" t="s">
         <v>60</v>
       </c>
       <c r="F26" s="9">
-        <f>MATCH(C26, A2:A7, 0)</f>
-        <v>4</v>
+        <f>MATCH(C26, A1:A7, 0)</f>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
@@ -2620,7 +2620,7 @@
         <v>55</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="D27" s="7"/>
       <c r="E27" t="s">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="F27" s="9">
         <f>MATCH(C27, A1:F1, 0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
@@ -2637,8 +2637,8 @@
         <v>53</v>
       </c>
       <c r="C28" s="10">
-        <f>INDEX(A2:F7, F26, F27)</f>
-        <v>2530</v>
+        <f>INDEX(A1:F7,F26,F27)</f>
+        <v>46</v>
       </c>
       <c r="D28" s="7"/>
     </row>
@@ -2648,8 +2648,8 @@
         <v>56</v>
       </c>
       <c r="C29" s="11">
-        <f>INDEX(A2:F7, MATCH(C26, A2:A7, 0), MATCH(C27, A1:F1, 0))</f>
-        <v>2530</v>
+        <f>INDEX(A1:F7, MATCH(C26, A1:A7, 0), MATCH(C27, A1:F1, 0))</f>
+        <v>46</v>
       </c>
       <c r="D29" s="7"/>
     </row>
@@ -2693,36 +2693,36 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D2" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="12" t="s">
         <v>66</v>
       </c>
       <c r="G2" t="s">
         <v>72</v>
       </c>
       <c r="H2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C3" s="15">
+      <c r="C3" s="13">
         <v>200</v>
       </c>
-      <c r="D3" s="15">
+      <c r="D3" s="13">
         <v>97</v>
       </c>
-      <c r="E3" s="15">
+      <c r="E3" s="13">
         <v>98</v>
       </c>
       <c r="G3" t="s">
@@ -2740,16 +2740,16 @@
       </c>
     </row>
     <row r="4" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="C4" s="15">
+      <c r="C4" s="13">
         <v>20</v>
       </c>
-      <c r="D4" s="15">
+      <c r="D4" s="13">
         <v>22</v>
       </c>
-      <c r="E4" s="15">
+      <c r="E4" s="13">
         <v>21</v>
       </c>
       <c r="G4" t="s">
@@ -2757,48 +2757,48 @@
       </c>
       <c r="H4">
         <f>HLOOKUP(H2, Table_56[[#All],[SR Tendulkar]:[V Kohli]], K3, FALSE)</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B5" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" s="13">
+        <v>32</v>
+      </c>
+      <c r="D5" s="13">
+        <v>35</v>
+      </c>
+      <c r="E5" s="13">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B6" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" s="13">
         <v>100</v>
       </c>
-    </row>
-    <row r="5" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B5" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="C5" s="15">
-        <v>32</v>
-      </c>
-      <c r="D5" s="15">
-        <v>35</v>
-      </c>
-      <c r="E5" s="15">
+      <c r="D6" s="13">
         <v>25</v>
       </c>
-    </row>
-    <row r="6" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B6" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" s="15">
-        <v>100</v>
-      </c>
-      <c r="D6" s="15">
-        <v>25</v>
-      </c>
-      <c r="E6" s="15">
+      <c r="E6" s="13">
         <v>54</v>
       </c>
     </row>
     <row r="7" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="C7" s="15">
+      <c r="C7" s="13">
         <v>125</v>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="13">
         <v>20</v>
       </c>
-      <c r="E7" s="15">
+      <c r="E7" s="13">
         <v>14</v>
       </c>
     </row>
